--- a/ig/improve-doc/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/improve-doc/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2024-10-01</t>
+    <t>2024-11-05</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-01T00:00:00+00:00</t>
+    <t>2024-11-06T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41159</t>
+    <t>41241</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/improve-doc/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/improve-doc/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2024-11-05</t>
+    <t>2024-12-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T00:00:00+00:00</t>
+    <t>2024-12-03T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41241</t>
+    <t>41204</t>
   </si>
   <si>
     <t>Code</t>
